--- a/TrackData.xlsx
+++ b/TrackData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosa\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9A844E1-BCB8-4105-8BBD-2E76AF2ED81D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96C22826-01B4-4343-8C60-14F605E4E546}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{905439D2-1156-4C4C-9326-B017DE0028B0}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="74">
   <si>
     <t>Sl#</t>
   </si>
@@ -161,6 +161,9 @@
     <t>SH1</t>
   </si>
   <si>
+    <t>SH2</t>
+  </si>
+  <si>
     <t>8 HRS</t>
   </si>
   <si>
@@ -243,6 +246,18 @@
   </si>
   <si>
     <t>Progressing</t>
+  </si>
+  <si>
+    <t>TrackData.xlsx</t>
+  </si>
+  <si>
+    <t>Task Priority</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>Low</t>
   </si>
 </sst>
 </file>
@@ -299,7 +314,19 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="7">
+    <dxf>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
     </dxf>
@@ -310,15 +337,6 @@
           <bgColor rgb="FFFFFF00"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
     </dxf>
     <dxf>
       <fill>
@@ -342,11 +360,11 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5290E8BE-3AD5-4226-B135-54B5E8934B24}" name="Table1" displayName="Table1" ref="A1:S11" totalsRowShown="0">
-  <autoFilter ref="A1:S11" xr:uid="{5290E8BE-3AD5-4226-B135-54B5E8934B24}"/>
-  <tableColumns count="19">
-    <tableColumn id="1" xr3:uid="{72BC517A-C330-4D2C-B716-7CD54896F502}" name="Sl#" dataDxfId="5"/>
-    <tableColumn id="19" xr3:uid="{AC837E95-ADE8-4D87-8BC5-D94E4DB5CB56}" name="Period" dataDxfId="1"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5290E8BE-3AD5-4226-B135-54B5E8934B24}" name="Table1" displayName="Table1" ref="A1:U11" totalsRowShown="0">
+  <autoFilter ref="A1:U11" xr:uid="{5290E8BE-3AD5-4226-B135-54B5E8934B24}"/>
+  <tableColumns count="21">
+    <tableColumn id="1" xr3:uid="{72BC517A-C330-4D2C-B716-7CD54896F502}" name="Sl#" dataDxfId="6"/>
+    <tableColumn id="19" xr3:uid="{AC837E95-ADE8-4D87-8BC5-D94E4DB5CB56}" name="Period" dataDxfId="5"/>
     <tableColumn id="2" xr3:uid="{1ED56A7E-FECC-4F51-ACDC-5840B83A28B2}" name="Emp Name"/>
     <tableColumn id="3" xr3:uid="{A52F05A5-DB73-4FC3-89C6-116636475603}" name="Department"/>
     <tableColumn id="4" xr3:uid="{064229FE-28F0-4193-A693-BB12AEC964F1}" name="Reporting"/>
@@ -355,15 +373,17 @@
     <tableColumn id="7" xr3:uid="{47E169B2-05D0-4AC2-87E5-1B2C3F07387E}" name="Work Avilability"/>
     <tableColumn id="8" xr3:uid="{3BEE1C15-E6CA-4C5C-87EB-71DC65E877AA}" name="Working HR"/>
     <tableColumn id="9" xr3:uid="{C201BDDE-403A-45DE-A795-EDE84E8E9370}" name="Work HRS"/>
-    <tableColumn id="10" xr3:uid="{70B1FB55-E90D-4A63-923C-04F838533FBD}" name="Task"/>
+    <tableColumn id="21" xr3:uid="{9D833A83-7B3C-486B-AA60-4D142871FAD2}" name="Task Priority"/>
+    <tableColumn id="13" xr3:uid="{67891364-A003-4055-A747-DDA87FCEF333}" name="Task Type"/>
     <tableColumn id="11" xr3:uid="{26BCC400-8649-4FAA-96E7-EC670DF4B19C}" name="Task Assigned Date" dataDxfId="4"/>
     <tableColumn id="12" xr3:uid="{D54B625F-FCD4-4751-A534-862B0B260FCC}" name="Task Posted"/>
-    <tableColumn id="13" xr3:uid="{67891364-A003-4055-A747-DDA87FCEF333}" name="Task Type"/>
     <tableColumn id="14" xr3:uid="{EF3DF20B-950C-4360-8B0B-E926974EC92C}" name="Task Assigned"/>
     <tableColumn id="15" xr3:uid="{6F1FA8E4-CA92-48BE-9CF4-77848152C3D4}" name="Task Taken"/>
-    <tableColumn id="16" xr3:uid="{CB8396CC-7B62-465C-B7A7-0CEA80FDB369}" name="Task Taken Date" dataDxfId="0"/>
-    <tableColumn id="18" xr3:uid="{BAFBFA9F-8228-4488-8AEA-C49F22BF4973}" name="Task Progress" dataDxfId="3"/>
-    <tableColumn id="17" xr3:uid="{C629D2DC-E6E4-4DD1-B35A-F685D8858C9F}" name="Task Completed date" dataDxfId="2"/>
+    <tableColumn id="16" xr3:uid="{CB8396CC-7B62-465C-B7A7-0CEA80FDB369}" name="Task Taken Date" dataDxfId="3"/>
+    <tableColumn id="18" xr3:uid="{BAFBFA9F-8228-4488-8AEA-C49F22BF4973}" name="Task Progress" dataDxfId="2"/>
+    <tableColumn id="10" xr3:uid="{70B1FB55-E90D-4A63-923C-04F838533FBD}" name="Task"/>
+    <tableColumn id="17" xr3:uid="{C629D2DC-E6E4-4DD1-B35A-F685D8858C9F}" name="Task Completed date" dataDxfId="1"/>
+    <tableColumn id="22" xr3:uid="{D1CB8C1F-58BD-4990-9B61-981CC0338E77}" name="TrackData.xlsx" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -686,34 +706,35 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4DB6E2B-0127-42C4-A533-2F0E6ED23653}">
-  <dimension ref="A1:S11"/>
+  <dimension ref="A1:U11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="5.578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.05078125" customWidth="1"/>
     <col min="3" max="3" width="11.7890625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.1015625" customWidth="1"/>
-    <col min="5" max="5" width="10.41796875" customWidth="1"/>
+    <col min="5" max="5" width="6.05078125" customWidth="1"/>
     <col min="7" max="7" width="12.578125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.5234375" customWidth="1"/>
     <col min="9" max="9" width="12" customWidth="1"/>
     <col min="10" max="10" width="10.41796875" customWidth="1"/>
-    <col min="11" max="11" width="11.5234375" customWidth="1"/>
-    <col min="12" max="12" width="18.3125" customWidth="1"/>
-    <col min="13" max="13" width="12.3671875" customWidth="1"/>
-    <col min="14" max="14" width="10.5234375" customWidth="1"/>
-    <col min="15" max="15" width="14.20703125" customWidth="1"/>
-    <col min="16" max="16" width="11.47265625" customWidth="1"/>
-    <col min="17" max="18" width="15.7890625" customWidth="1"/>
-    <col min="19" max="19" width="13.9453125" customWidth="1"/>
+    <col min="12" max="12" width="12.3671875" customWidth="1"/>
+    <col min="13" max="13" width="11.5234375" customWidth="1"/>
+    <col min="14" max="14" width="18.3125" customWidth="1"/>
+    <col min="16" max="16" width="10.5234375" customWidth="1"/>
+    <col min="17" max="17" width="14.20703125" customWidth="1"/>
+    <col min="18" max="18" width="11.47265625" customWidth="1"/>
+    <col min="19" max="20" width="15.7890625" customWidth="1"/>
+    <col min="21" max="21" width="11.5234375" customWidth="1"/>
+    <col min="22" max="22" width="13.9453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
@@ -731,43 +752,49 @@
         <v>13</v>
       </c>
       <c r="H1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I1" t="s">
         <v>39</v>
       </c>
       <c r="J1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K1" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="L1" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="M1" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="N1" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="O1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="P1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="R1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="S1" t="s">
-        <v>64</v>
+        <v>44</v>
+      </c>
+      <c r="T1" t="s">
+        <v>65</v>
+      </c>
+      <c r="U1" t="s">
+        <v>70</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -796,35 +823,39 @@
         <v>40</v>
       </c>
       <c r="J2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K2" t="s">
-        <v>44</v>
-      </c>
-      <c r="L2" s="2">
+        <v>72</v>
+      </c>
+      <c r="L2" t="s">
+        <v>48</v>
+      </c>
+      <c r="M2" s="2">
         <v>45748</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>5</v>
-      </c>
-      <c r="N2" t="s">
-        <v>47</v>
       </c>
       <c r="O2" t="s">
         <v>9</v>
       </c>
       <c r="P2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Q2" s="2">
         <v>45748</v>
       </c>
       <c r="R2" t="s">
-        <v>68</v>
-      </c>
-      <c r="S2" s="2"/>
+        <v>69</v>
+      </c>
+      <c r="S2" t="s">
+        <v>45</v>
+      </c>
+      <c r="T2" s="2"/>
+      <c r="U2" s="2"/>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -853,35 +884,39 @@
         <v>40</v>
       </c>
       <c r="J3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K3" t="s">
-        <v>44</v>
-      </c>
-      <c r="L3" s="2">
+        <v>73</v>
+      </c>
+      <c r="L3" t="s">
+        <v>49</v>
+      </c>
+      <c r="M3" s="2">
         <v>45748</v>
       </c>
-      <c r="M3" t="s">
+      <c r="N3" t="s">
         <v>8</v>
-      </c>
-      <c r="N3" t="s">
-        <v>48</v>
       </c>
       <c r="O3" t="s">
         <v>9</v>
       </c>
       <c r="P3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Q3" s="2">
         <v>45748</v>
       </c>
       <c r="R3" t="s">
-        <v>68</v>
-      </c>
-      <c r="S3" s="2"/>
+        <v>69</v>
+      </c>
+      <c r="S3" t="s">
+        <v>45</v>
+      </c>
+      <c r="T3" s="2"/>
+      <c r="U3" s="2"/>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -910,35 +945,39 @@
         <v>40</v>
       </c>
       <c r="J4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K4" t="s">
-        <v>44</v>
-      </c>
-      <c r="L4" s="2">
+        <v>73</v>
+      </c>
+      <c r="L4" t="s">
+        <v>50</v>
+      </c>
+      <c r="M4" s="2">
         <v>45752</v>
       </c>
-      <c r="M4" t="s">
+      <c r="N4" t="s">
         <v>9</v>
-      </c>
-      <c r="N4" t="s">
-        <v>49</v>
       </c>
       <c r="O4" t="s">
         <v>9</v>
       </c>
       <c r="P4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Q4" s="2">
         <v>45752</v>
       </c>
       <c r="R4" t="s">
-        <v>68</v>
-      </c>
-      <c r="S4" s="2"/>
+        <v>69</v>
+      </c>
+      <c r="S4" t="s">
+        <v>45</v>
+      </c>
+      <c r="T4" s="2"/>
+      <c r="U4" s="2"/>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -967,35 +1006,39 @@
         <v>40</v>
       </c>
       <c r="J5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K5" t="s">
-        <v>44</v>
-      </c>
-      <c r="L5" s="2">
+        <v>72</v>
+      </c>
+      <c r="L5" t="s">
+        <v>51</v>
+      </c>
+      <c r="M5" s="2">
         <v>45752</v>
       </c>
-      <c r="M5" t="s">
+      <c r="N5" t="s">
         <v>11</v>
-      </c>
-      <c r="N5" t="s">
-        <v>50</v>
       </c>
       <c r="O5" t="s">
         <v>9</v>
       </c>
       <c r="P5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Q5" s="2">
         <v>45753</v>
       </c>
       <c r="R5" t="s">
-        <v>68</v>
-      </c>
-      <c r="S5" s="2"/>
+        <v>69</v>
+      </c>
+      <c r="S5" t="s">
+        <v>45</v>
+      </c>
+      <c r="T5" s="2"/>
+      <c r="U5" s="2"/>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1024,37 +1067,41 @@
         <v>40</v>
       </c>
       <c r="J6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K6" t="s">
-        <v>44</v>
-      </c>
-      <c r="L6" s="2">
+        <v>72</v>
+      </c>
+      <c r="L6" t="s">
+        <v>52</v>
+      </c>
+      <c r="M6" s="2">
         <v>45752</v>
       </c>
-      <c r="M6" t="s">
+      <c r="N6" t="s">
         <v>3</v>
-      </c>
-      <c r="N6" t="s">
-        <v>51</v>
       </c>
       <c r="O6" t="s">
         <v>9</v>
       </c>
       <c r="P6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Q6" s="2">
         <v>45753</v>
       </c>
       <c r="R6" t="s">
-        <v>60</v>
-      </c>
-      <c r="S6" s="2">
+        <v>61</v>
+      </c>
+      <c r="S6" t="s">
+        <v>45</v>
+      </c>
+      <c r="T6" s="2">
         <v>45753</v>
       </c>
+      <c r="U6" s="2"/>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -1080,40 +1127,44 @@
         <v>37</v>
       </c>
       <c r="I7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K7" t="s">
-        <v>44</v>
-      </c>
-      <c r="L7" s="2">
+        <v>73</v>
+      </c>
+      <c r="L7" t="s">
+        <v>53</v>
+      </c>
+      <c r="M7" s="2">
         <v>45752</v>
       </c>
-      <c r="M7" t="s">
+      <c r="N7" t="s">
         <v>2</v>
-      </c>
-      <c r="N7" t="s">
-        <v>52</v>
       </c>
       <c r="O7" t="s">
         <v>7</v>
       </c>
       <c r="P7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Q7" s="2">
         <v>45753</v>
       </c>
       <c r="R7" t="s">
-        <v>60</v>
-      </c>
-      <c r="S7" s="2">
+        <v>61</v>
+      </c>
+      <c r="S7" t="s">
+        <v>45</v>
+      </c>
+      <c r="T7" s="2">
         <v>45754</v>
       </c>
+      <c r="U7" s="2"/>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -1139,40 +1190,44 @@
         <v>37</v>
       </c>
       <c r="I8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K8" t="s">
-        <v>44</v>
-      </c>
-      <c r="L8" s="2">
+        <v>72</v>
+      </c>
+      <c r="L8" t="s">
+        <v>54</v>
+      </c>
+      <c r="M8" s="2">
         <v>45748</v>
       </c>
-      <c r="M8" t="s">
+      <c r="N8" t="s">
         <v>7</v>
-      </c>
-      <c r="N8" t="s">
-        <v>53</v>
       </c>
       <c r="O8" t="s">
         <v>7</v>
       </c>
       <c r="P8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Q8" s="2">
         <v>45757</v>
       </c>
       <c r="R8" t="s">
-        <v>60</v>
-      </c>
-      <c r="S8" s="2">
+        <v>61</v>
+      </c>
+      <c r="S8" t="s">
+        <v>45</v>
+      </c>
+      <c r="T8" s="2">
         <v>45762</v>
       </c>
+      <c r="U8" s="2"/>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -1198,38 +1253,42 @@
         <v>37</v>
       </c>
       <c r="I9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K9" t="s">
-        <v>44</v>
-      </c>
-      <c r="L9" s="2">
+        <v>72</v>
+      </c>
+      <c r="L9" t="s">
+        <v>48</v>
+      </c>
+      <c r="M9" s="2">
         <v>45748</v>
       </c>
-      <c r="M9" t="s">
+      <c r="N9" t="s">
         <v>8</v>
-      </c>
-      <c r="N9" t="s">
-        <v>47</v>
       </c>
       <c r="O9" t="s">
         <v>7</v>
       </c>
       <c r="P9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q9" s="2"/>
       <c r="R9" t="s">
-        <v>58</v>
-      </c>
-      <c r="S9" s="2">
+        <v>59</v>
+      </c>
+      <c r="S9" t="s">
+        <v>45</v>
+      </c>
+      <c r="T9" s="2">
         <v>45756</v>
       </c>
+      <c r="U9" s="2"/>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -1255,38 +1314,42 @@
         <v>38</v>
       </c>
       <c r="I10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K10" t="s">
-        <v>44</v>
-      </c>
-      <c r="L10" s="2">
+        <v>72</v>
+      </c>
+      <c r="L10" t="s">
+        <v>55</v>
+      </c>
+      <c r="M10" s="2">
         <v>45748</v>
       </c>
-      <c r="M10" t="s">
+      <c r="N10" t="s">
         <v>2</v>
-      </c>
-      <c r="N10" t="s">
-        <v>54</v>
       </c>
       <c r="O10" t="s">
         <v>7</v>
       </c>
       <c r="P10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q10" s="2"/>
       <c r="R10" t="s">
-        <v>58</v>
-      </c>
-      <c r="S10" s="2">
+        <v>59</v>
+      </c>
+      <c r="S10" t="s">
+        <v>45</v>
+      </c>
+      <c r="T10" s="2">
         <v>45756</v>
       </c>
+      <c r="U10" s="2"/>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -1312,27 +1375,28 @@
         <v>38</v>
       </c>
       <c r="I11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J11" t="s">
-        <v>41</v>
-      </c>
-      <c r="K11" t="s">
-        <v>45</v>
-      </c>
-      <c r="L11" s="2">
+        <v>42</v>
+      </c>
+      <c r="M11" s="2">
         <v>45748</v>
       </c>
       <c r="P11" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q11" s="2"/>
       <c r="R11" t="s">
-        <v>58</v>
-      </c>
-      <c r="S11" s="2">
+        <v>59</v>
+      </c>
+      <c r="S11" t="s">
+        <v>46</v>
+      </c>
+      <c r="T11" s="2">
         <v>45756</v>
       </c>
+      <c r="U11" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
